--- a/docs/test-cases/SPM-43_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-43_Test_Cases.xlsx
@@ -22,6 +22,8 @@
     <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="TC13" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="TC14" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="TC15" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TC16" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -461,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -735,7 +737,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -968,81 +970,146 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>TC15</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>SPM-43-TC15</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>A request for an event that has not been approved yet is not shown to Venue Staff</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>AC1</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>TC16</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>SPM-43-TC16</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>A request in the first slot clear of an approved booking's turnaround is not in conflict and can be approved</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>AC3, AC7</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Covered by</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="17.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Venue Staff can view pending booking requests.</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>SPM-43-TC01</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="31" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>AC2</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>The request displays the requested venue, date, time and event information.</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="9" t="n"/>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>SPM-43-TC01
-SPM-43-TC02</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Covered by</t>
         </is>
       </c>
       <c r="F22" s="9" t="n"/>
     </row>
-    <row r="23" ht="112" customHeight="1">
+    <row r="23" ht="31" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>AC3</t>
+          <t>AC1</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Venue Staff can approve the request.</t>
+          <t>Venue Staff can view pending booking requests.</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>SPM-43-TC01
+SPM-43-TC15</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="31" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>AC2</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>The request displays the requested venue, date, time and event information.</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>SPM-43-TC01
+SPM-43-TC02</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="125.5" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>AC3</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Venue Staff can approve the request.</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>SPM-43-TC03
 SPM-43-TC04
@@ -1051,104 +1118,106 @@
 SPM-43-TC11
 SPM-43-TC12
 SPM-43-TC13
-SPM-43-TC14</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="44.5" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+SPM-43-TC14
+SPM-43-TC16</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="44.5" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Venue Staff can reject the request.</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>SPM-43-TC08
 SPM-43-TC11
 SPM-43-TC12</t>
         </is>
       </c>
-      <c r="F24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="31" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="31" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Venue Staff can provide a reason when rejecting a request.</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>SPM-43-TC07
-SPM-43-TC08</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="n"/>
-    </row>
-    <row r="26" ht="31" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>AC6</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Venue Staff can suggest an alternative venue or arrangement when rejecting a request, for the Coordinator to review and act on.</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>SPM-43-TC09
-SPM-43-TC10</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="44.5" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>An approved booking request becomes a Confirmed booking — the same status referenced by Detect Venue Booking Conflicts and View Venue Availability.</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
+          <t>SPM-43-TC07
+SPM-43-TC08</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="31" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Venue Staff can suggest an alternative venue or arrangement when rejecting a request, for the Coordinator to review and act on.</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>SPM-43-TC09
+SPM-43-TC10</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>AC7</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>An approved booking request becomes a Confirmed booking — the same status referenced by Detect Venue Booking Conflicts and View Venue Availability.</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
           <t>SPM-43-TC03
 SPM-43-TC04
-SPM-43-TC05</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="n"/>
-    </row>
-    <row r="29" ht="301" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+SPM-43-TC05
+SPM-43-TC16</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n"/>
+    </row>
+    <row r="31" ht="301" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>src/app/bookings/page.tsx
 src/app/api/venue-bookings/route.ts
@@ -1174,16 +1243,15 @@
 prisma/seed.ts</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="9" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E29:F29"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B22:D22"/>
@@ -1193,12 +1261,13 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1215,6 +1284,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2432,13 +2503,345 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-43-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="166" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
+Seed: 'SPM43 Policy Briefing' (status Under review, 09:00-12:00 on 18 May 2027) has a Pending request for Orchard Studio (ORC-STU) on 18 May 2027, AM. The app no longer lets a Coordinator make a request before the event is approved (SPM-54), so this one is created by the fixture script and stands for a request made before that rule.
+If it is missing, or no longer Pending because an earlier run was not reset, run: npm run fixtures:spm43 (adds or resets the SPM43 test data without a reseed).
+This case changes no data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Log in as marcus.wong@connectsphere.com / password123
+2. Click 'Booking Requests' in the sidebar
+3. Look through the whole list for a card for 'SPM43 Policy Briefing'
+4. Look through the list for any card whose line under 'Requested by' reads 'Event is Submitted' or 'Event is Under review'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Request: SPM43 Policy Briefing at Orchard Studio (ORC-STU), 18 May 2027, AM
+Event status: Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: There is no card for 'SPM43 Policy Briefing', although its request is Pending - a request waits for its event to be approved before Venue Staff see it.
+Step 4: There is no such card: every request listed belongs to an event that is past approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kayalvizhi24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-43-TC16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="193" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
+Seed: 'SPM43 Board Strategy Day' has an Approved booking at Marina Auditorium (MAR-AUD, setup 60 min, teardown 30 min) on 7 May 2027, AM + PM, so its turnaround takes 7 May Night. 'SPM43 Alumni Lecture' (status Planning, 14:00-17:00 on 8 May 2027) has a Pending request for Marina Auditorium on 8 May 2027, PM only; its own setup takes 8 May AM, the slot straight after that turnaround.
+If it is missing, or no longer Pending because an earlier run was not reset, run: npm run fixtures:spm43 (adds or resets the SPM43 test data without a reseed).
+This case changes no data: the approval is cancelled in step 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Log in as marcus.wong@connectsphere.com / password123
+2. Click 'Booking Requests' in the sidebar
+3. Find the 'SPM43 Alumni Lecture' card and check its Requested slot, the Setup and Turnaround lines under it, and its badge
+4. Click 'Approve' on the 'SPM43 Alumni Lecture' card
+5. In the dialog, click 'Cancel'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Pending: SPM43 Alumni Lecture, Marina Auditorium, 8 May 2027, PM (setup: 8 May AM)
+Approved: SPM43 Board Strategy Day, Marina Auditorium, 7 May 2027, AM + PM (turnaround: 7 May Night)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Step 3: Requested reads '8 May 2027 · PM (13:00–18:00)', with 'Setup: 8 May 2027 AM (07:00–12:00)' and 'Turnaround: 8 May 2027 Night (19:00–24:00)' under it. The badge reads 'Pending', not 'Conflict', and the card has no red message.
+Step 4: The 'Approve this booking?' dialog opens, naming Marina Auditorium (MAR-AUD) and '8 May 2027 · PM (13:00–18:00)' - the request can be approved.
+Step 5: The dialog closes. The card is still in the list with the badge 'Pending' and nothing has been booked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kayalvizhi24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2469,76 +2872,21 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-10-02 (Kayal): the booking's badge reads 'Approved', as in the BPMN (docs/ConnectSphere_BPMN.drawio, gateway 'Booking approved?' -&gt; 'approved'). AC7's 'Confirmed booking' is that approved booking: the stored status is 'approved', which the availability calendar (SPM-46) shows as 'Booked' and conflict detection (SPM-44) blocks on (TC03, TC04). 'Confirmed' stays an event status only ('Confirm event' is the Coordinator's later step in both diagrams), so a booking is never labelled 'Confirmed'.</t>
+          <t>Reverting: a case that approves or rejects says so in its Preconditions ('This case changes data: run npm run fixtures:spm43 once when you finish testing …'). That command is the only reset needed and is never a reseed - it resets only the 'SPM43 …' events in place (their booking requests and decisions are dropped and recreated; each event keeps its EVT- reference), makes 'SPM43 Retire Test Room' active again and resets 'SPM43 Maintenance Room' to its one maintenance period. Nothing outside the SPM43 test data is changed by any case.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-18 (Kristen, Jira comment on SPM-43): notifying the Coordinator of the outcome is out of scope - notifications belong to SPM-53. No test case covers a notification, and the decision route writes none (removed 2026-10-02). The Coordinator finds the decision, reason and suggestion on the event's Venue tab (TC03, TC08, TC09, TC10).</t>
+          <t>Fixtures: scripts/seed-spm43.ts creates fourteen 'SPM43 …' events in May 2027, on base-seed venues plus the two test venues SPM43-MNT and SPM43-RET; prisma/seed.ts creates the same rows. Each event keeps its EVT- reference between runs on one database, but the number differs from one database to another, so the cases name events by title and never ask the tester to type an event address.</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
-    </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-10-02 (Kayal): the suggestion is an optional venue picker plus an optional free-text 'Alternative arrangement'. It is a suggestion only - nothing is booked or requested (customer #45, #110); the Coordinator submits a new request, which SPM-42 already tests.</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n"/>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-10-02: a refusal whose request has left the list (SPM-43-TC12, decided in another tab) is shown at the top of the Booking Requests page instead of on the card.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="98.5" customHeight="1">
-      <c r="A6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>RESOLVED 2026-10-02 (Kayal): approval blocked by an unavailable venue and by a retired venue are tested by hand (TC13, TC14), each on its own test venue so no other tester's data is touched. Venue Staff can retire and restore a venue in the app, so TC14 does both itself. Recording an unavailability period has no screen yet (Block venue, S-23 - DOCUMENTATION.md Known Gaps), so TC13's period is created by the fixture script.</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="112" customHeight="1">
-      <c r="A7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Reverting: a case that approves or rejects says so in its Preconditions ('This case changes data: run npm run fixtures:spm43 once when you finish testing …'). That command is the only reset needed and is never a reseed - it resets only the 'SPM43 …' events in place (their booking requests and decisions are dropped and recreated; each event keeps its EVT- reference), makes 'SPM43 Retire Test Room' active again and resets 'SPM43 Maintenance Room' to its one maintenance period. Nothing outside the SPM43 test data is changed by any case.</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="85" customHeight="1">
-      <c r="A8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Fixtures: scripts/seed-spm43.ts creates twelve 'SPM43 …' events in May 2027, on base-seed venues plus the two test venues SPM43-MNT and SPM43-RET; prisma/seed.ts creates the same rows. Each event keeps its EVT- reference between runs on one database, but the number differs from one database to another, so the cases name events by title and never ask the tester to type an event address.</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2752,7 +3100,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
-Seed: 'SPM43 Two-Day Forum' (status Approved, 60 people, Theatre, 11 May 2027 09:00 to 12 May 2027 17:00) has a session 'Day 2' (30 people, Classroom, 14:00-17:00 on 12 May 2027) with a Pending request for Jurong Training Room (JUR-TRN, setup 45 min, teardown 30 min).
+Seed: 'SPM43 Two-Day Forum' (status Planning, 60 people, Theatre, 11 May 2027 09:00 to 12 May 2027 17:00) has a session 'Day 2' (30 people, Classroom, 14:00-17:00 on 12 May 2027) with a Pending request for Jurong Training Room (JUR-TRN, setup 45 min, teardown 30 min).
 If it is missing, or no longer Pending because an earlier run was not reset, run: npm run fixtures:spm43 (adds or resets the SPM43 test data without a reseed).</t>
         </is>
       </c>
@@ -2792,7 +3140,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Step 3: The card shows 'Session: Day 2'. Requested is '12 May 2027 · PM (13:00–18:00)' with 'Setup: 12 May 2027 AM (07:00–12:00)' and 'Turnaround: 12 May 2027 Night (19:00–24:00)'. The time is labelled 'Session time' and reads '12 May 2027, 14:00–17:00' (not the event's two days). Layout is 'Classroom' and Expected attendance is '30' (the session's, not the event's Theatre and 60). Venue requirements is 'Tables in rows, power at every seat.' and 'Event is Approved' is shown under Requested by.</t>
+          <t>Step 3: The card shows 'Session: Day 2'. Requested is '12 May 2027 · PM (13:00–18:00)' with 'Setup: 12 May 2027 AM (07:00–12:00)' and 'Turnaround: 12 May 2027 Night (19:00–24:00)'. The time is labelled 'Session time' and reads '12 May 2027, 14:00–17:00' (not the event's two days). Layout is 'Classroom' and Expected attendance is '30' (the session's, not the event's Theatre and 60). Venue requirements is 'Tables in rows, power at every seat.' and 'Event is Planning' is shown under Requested by.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-43_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-43_Test_Cases.xlsx
@@ -494,12 +494,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="21">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>SPM-43: As Venue Staff, I want to review a venue booking request so that I can decide whether the requested venue can be made available for the event</t>
         </is>
@@ -511,32 +511,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -563,27 +563,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC01</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Venue Staff see the pending requests, each with its venue, date, slots and event details</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -606,27 +606,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC02</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>A request for one session shows that session's own time, attendance and layout, not the event's</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -649,27 +649,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC03</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Approving a request books the room: it leaves the list, the calendar shows it Booked, and the Coordinator sees it Approved</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>AC3, AC7</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -692,27 +692,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC04</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Once one of two requests for the same room and slot is approved, the other is in conflict and cannot be approved</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>AC7, AC3</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -735,27 +735,27 @@
           <t>RETIRED – TC05</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC05</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>A request that clashes only through an approved booking's turnaround slot cannot be approved</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>AC7, AC3</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -782,27 +782,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC06</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>A request for an event that has since been cancelled cannot be approved</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -825,27 +825,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC07</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Rejecting without a reason, or with only spaces, is refused</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -868,27 +868,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC08</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Rejecting with a reason takes the request off the list and shows the Coordinator the reason</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>AC4, AC5</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -911,27 +911,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC09</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Venue Staff suggest another venue when rejecting; the Coordinator sees it and can start a new request for that venue</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -954,27 +954,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC10</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Venue Staff suggest an alternative arrangement in words, without naming a venue</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -997,27 +997,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC11</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Only Venue Staff can open Booking Requests or decide a request</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>AC3, AC4</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1036,27 +1036,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC12</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>A request is decided once: approving one that was already rejected from another tab is refused</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>AC3, AC4</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1079,27 +1079,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC13</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>A request for a time when the venue is unavailable (maintenance) cannot be approved</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1122,27 +1122,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC14</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>A request for a venue that has been retired cannot be approved</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1165,27 +1165,27 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC15</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>A request for an event that has not been approved yet is not shown to Venue Staff</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1208,27 +1208,27 @@
           <t>RETIRED – TC16</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC16</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>A request in the first slot clear of an approved booking's turnaround is not in conflict and can be approved</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>AC3, AC7</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1250,20 +1250,21 @@
       </c>
     </row>
     <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="15.75" customHeight="1" s="21">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C22" s="22" t="n"/>
       <c r="D22" s="23" t="n"/>
-      <c r="E22" s="1" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1271,19 +1272,19 @@
       <c r="F22" s="23" t="n"/>
     </row>
     <row r="23" ht="30.75" customHeight="1" s="21">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Venue Staff can view pending booking requests.</t>
         </is>
       </c>
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="23" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC01
 SPM-43-TC15</t>
@@ -1292,19 +1293,19 @@
       <c r="F23" s="23" t="n"/>
     </row>
     <row r="24" ht="30.75" customHeight="1" s="21">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>The request displays the requested venue, date, time and event information.</t>
         </is>
       </c>
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="23" t="n"/>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC01
 SPM-43-TC02</t>
@@ -1313,19 +1314,19 @@
       <c r="F24" s="23" t="n"/>
     </row>
     <row r="25" ht="111.75" customHeight="1" s="21">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Venue Staff can approve the request.</t>
         </is>
       </c>
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC03
 SPM-43-TC04
@@ -1340,19 +1341,19 @@
       <c r="F25" s="23" t="n"/>
     </row>
     <row r="26" ht="44.25" customHeight="1" s="21">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Venue Staff can reject the request.</t>
         </is>
       </c>
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC08
 SPM-43-TC11
@@ -1362,19 +1363,19 @@
       <c r="F26" s="23" t="n"/>
     </row>
     <row r="27" ht="30.75" customHeight="1" s="21">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>Venue Staff can provide a reason when rejecting a request.</t>
         </is>
       </c>
       <c r="C27" s="22" t="n"/>
       <c r="D27" s="23" t="n"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC07
 SPM-43-TC08</t>
@@ -1383,19 +1384,19 @@
       <c r="F27" s="23" t="n"/>
     </row>
     <row r="28" ht="30.75" customHeight="1" s="21">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Venue Staff can suggest an alternative venue or arrangement when rejecting a request, for the Coordinator to review and act on.</t>
         </is>
       </c>
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="23" t="n"/>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC09
 SPM-43-TC10</t>
@@ -1404,19 +1405,19 @@
       <c r="F28" s="23" t="n"/>
     </row>
     <row r="29" ht="44.25" customHeight="1" s="21">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>An approved booking request becomes a Confirmed booking — the same status referenced by Detect Venue Booking Conflicts and View Venue Availability.</t>
         </is>
       </c>
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="23" t="n"/>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC03
 SPM-43-TC04
@@ -1427,12 +1428,12 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" s="21"/>
     <row r="31" ht="300.75" customHeight="1" s="21">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>src/app/bookings/page.tsx
 src/app/api/venue-bookings/route.ts
@@ -2512,7 +2513,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC09</t>
         </is>
@@ -2524,7 +2525,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Awards Dinner' (status Planning, coordinator Daniel Tan, 80 people, Banquet, 19:00-22:00 on 6 May 2027) has a Pending request for Orchard Gallery (ORC-GAL) on 6 May 2027, Night.
@@ -2539,7 +2540,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -2562,7 +2563,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Awards Dinner at Orchard Gallery (ORC-GAL), 6 May 2027, Night
 Reason for rejection: Gallery is closed for a private hire that evening.
@@ -2577,7 +2578,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 5: The list starts with 'No venue suggested' and offers the other venues, but not 'Orchard Gallery (ORC-GAL)' - the room being refused cannot be the suggestion.
 Step 7: A green 'Booking request rejected' message appears and the 'SPM43 Awards Dinner' card leaves the list.
@@ -2592,7 +2593,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -2624,7 +2625,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 5: The list starts with 'No venue suggested' and offers the other venues, but not 'Orchard Gallery (ORC-GAL)' - the room being refused cannot be the suggestion.
 Step 7: A green 'Booking request rejected' message appears and the 'SPM43 Awards Dinner' card leaves the list.
@@ -2694,7 +2695,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 5: The list starts with 'No venue suggested' and offers the other venues, but not 'Orchard Gallery (ORC-GAL)' - the room being refused cannot be the suggestion.
 Step 7: A green 'Booking request rejected' message appears and the 'SPM43 Awards Dinner' card leaves the list.
@@ -3770,7 +3771,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC10</t>
         </is>
@@ -3782,7 +3783,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Investor Update' (status Planning, coordinator Daniel Tan, 14:00-16:00 on 8 May 2027) has a Pending request for One-North Auditorium (ONE-AUD) on 8 May 2027, PM.
@@ -3797,7 +3798,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -3819,7 +3820,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Investor Update at One-North Auditorium (ONE-AUD), 8 May 2027, PM
 Reason for rejection: Auditorium is reserved for a recording session that afternoon.
@@ -3834,7 +3835,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 7: A green 'Booking request rejected' message appears and the 'SPM43 Investor Update' card leaves the list.
 Step 11: Under 'Booking requests', the One-North Auditorium (ONE-AUD) request has the badge 'Rejected' and shows 'Reason from Venue Staff: Auditorium is reserved for a recording session that afternoon.' and 'Suggested alternative: The auditorium is free on 8 May 2027 in the AM slot.' There is no 'Request this venue' button, because no venue was suggested.</t>
@@ -3847,7 +3848,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -3879,7 +3880,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 7: A green 'Booking request rejected' message appears and the 'SPM43 Investor Update' card leaves the list.
 Step 11: Under 'Booking requests', the One-North Auditorium (ONE-AUD) request has the badge 'Rejected' and shows 'Reason from Venue Staff: Auditorium is reserved for a recording session that afternoon.' and 'Suggested alternative: The auditorium is free on 8 May 2027 in the AM slot.' There is no 'Request this venue' button, because no venue was suggested.</t>
@@ -3947,7 +3948,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 7: A green 'Booking request rejected' message appears and the 'SPM43 Investor Update' card leaves the list.
 Step 11: Under 'Booking requests', the One-North Auditorium (ONE-AUD) request has the badge 'Rejected' and shows 'Reason from Venue Staff: Auditorium is reserved for a recording session that afternoon.' and 'Suggested alternative: The auditorium is free on 8 May 2027 in the AM slot.' There is no 'Request this venue' button, because no venue was suggested.</t>
@@ -5014,7 +5015,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC11</t>
         </is>
@@ -5026,7 +5027,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Accounts (password123): Coordinator Daniel Tan (daniel.tan@connectsphere.com), Technical Support Kenji Sato (kenji.sato@connectsphere.com).
 Seed: 'SPM43 Evening Recital' (coordinator Daniel Tan) has a Pending request for Marina Auditorium (MAR-AUD).
@@ -5040,7 +5041,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>1. Log in as daniel.tan@connectsphere.com / password123
 2. Look through the sidebar for 'Booking Requests'
@@ -5059,7 +5060,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Accounts: Daniel Tan (Event Coordinator, the requester), Kenji Sato (Technical Support)</t>
         </is>
@@ -5071,7 +5072,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Step 2: The sidebar has Dashboard, Review Queue, All Events, Venues, Equipment and Notifications - no 'Booking Requests'.
 Step 3: The page shows 'You do not have access to this' with 'Reviewing venue bookings is Venue Staff's role.' and a 'Back to Dashboard' button. No booking request is shown.
@@ -5086,7 +5087,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -5118,7 +5119,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Step 2: The sidebar has Dashboard, Review Queue, All Events, Venues, Equipment and Notifications - no 'Booking Requests'.
 Step 3: The page shows 'You do not have access to this' with 'Reviewing venue bookings is Venue Staff's role.' and a 'Back to Dashboard' button. No booking request is shown.
@@ -5188,7 +5189,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Step 2: The sidebar has Dashboard, Review Queue, All Events, Venues, Equipment and Notifications - no 'Booking Requests'.
 Step 3: The page shows 'You do not have access to this' with 'Reviewing venue bookings is Venue Staff's role.' and a 'Back to Dashboard' button. No booking request is shown.
@@ -6262,7 +6263,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC12</t>
         </is>
@@ -6274,7 +6275,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Two-Day Forum' (coordinator Daniel Tan) has a session 'Day 1' (09:00-12:00 on 11 May 2027) with a Pending request for One-North Seminar Room (ONE-SEM) on 11 May 2027, AM.
@@ -6289,7 +6290,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -6312,7 +6313,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Two-Day Forum, session Day 1, at One-North Seminar Room (ONE-SEM), 11 May 2027, AM
 Reason for rejection: Seminar room is being repainted.</t>
@@ -6325,7 +6326,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 6: In the new tab a green 'Booking request rejected' message appears and the Day 1 card leaves the list.
 Step 7: The first tab still shows the Day 1 card, and the 'Approve this booking?' dialog opens.
@@ -6340,7 +6341,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -6372,7 +6373,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 6: In the new tab a green 'Booking request rejected' message appears and the Day 1 card leaves the list.
 Step 7: The first tab still shows the Day 1 card, and the 'Approve this booking?' dialog opens.
@@ -6442,7 +6443,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 6: In the new tab a green 'Booking request rejected' message appears and the Day 1 card leaves the list.
 Step 7: The first tab still shows the Day 1 card, and the 'Approve this booking?' dialog opens.
@@ -7518,7 +7519,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC13</t>
         </is>
@@ -7530,7 +7531,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Staff Briefing' (status Planning, 09:00-11:00 on 14 May 2027) has a Pending request for 'SPM43 Maintenance Room' (SPM43-MNT) on 14 May 2027, AM. That room is marked unavailable for maintenance all day on 14 May 2027.
@@ -7544,7 +7545,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -7560,7 +7561,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Staff Briefing at SPM43 Maintenance Room (SPM43-MNT), 14 May 2027, AM
 Venue unavailable: 14 May 2027, all day, maintenance</t>
@@ -7573,7 +7574,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 3: Requested reads '14 May 2027 · AM (07:00–12:00)'. The badge reads 'Conflict'. A red message titled 'This request cannot be approved as it stands' reads 'SPM43 Maintenance Room is unavailable at this time (maintenance).'
 Step 4: The 'Approve' button is greyed out and nothing happens - no dialog opens.
@@ -7587,7 +7588,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -7619,7 +7620,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 3: Requested reads '14 May 2027 · AM (07:00–12:00)'. The badge reads 'Conflict'. A red message titled 'This request cannot be approved as it stands' reads 'SPM43 Maintenance Room is unavailable at this time (maintenance).'
 Step 4: The 'Approve' button is greyed out and nothing happens - no dialog opens.
@@ -7688,7 +7689,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 3: Requested reads '14 May 2027 · AM (07:00–12:00)'. The badge reads 'Conflict'. A red message titled 'This request cannot be approved as it stands' reads 'SPM43 Maintenance Room is unavailable at this time (maintenance).'
 Step 4: The 'Approve' button is greyed out and nothing happens - no dialog opens.
@@ -8742,10 +8743,11 @@
     <col width="12.63" customWidth="1" style="21" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="90" customHeight="1" s="21">
+    <row r="1" ht="165" customHeight="1" s="21">
       <c r="A1" s="26" t="inlineStr">
         <is>
-          <t>v2 (2026-10-19): Venue bookings are now made for a start and end time on a 15-minute grid (SPM-93, discussion #128, Week 7 Change #1). Read every AM / PM / Night slot in this case as the event's (or session's) own start and end times; setup and turnaround are the venue's minutes either side, not whole slots, and the calendar has one Schedule column instead of slot columns. The behaviour this case checks is unchanged.</t>
+          <t>v2 (2026-10-19): Venue bookings are now made for a start and end time on a 15-minute grid (SPM-93, discussion #128, Week 7 Change #1). Read every AM / PM / Night slot in this case as the event's (or session's) own start and end times; setup and turnaround are the venue's minutes either side, not whole slots, and the calendar has one Schedule column instead of slot columns. The behaviour this case checks is unchanged.
+v3 (2026-10-20): After a save that flags no booking, the venue page now reads 'No bookings were affected, so nobody needed to be notified.' instead of 'No approved bookings were affected, so nobody needed to be notified.' (SPM-80, Week 7 Change #1: changing a venue's setup or turnaround time now re-checks pending requests as well as approved bookings). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8765,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC14</t>
         </is>
@@ -8775,7 +8777,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Team Retrospective' (status Planning, 14:00-16:00 on 17 May 2027) has a Pending request for 'SPM43 Retire Test Room' (SPM43-RET) on 17 May 2027, PM. That room is active and used by no other event.
@@ -8790,7 +8792,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Venues' in the sidebar
@@ -8813,7 +8815,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Venue: SPM43 Retire Test Room (SPM43-RET)
 Request: SPM43 Team Retrospective, 17 May 2027, PM</t>
@@ -8826,7 +8828,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 4: A dialog titled 'Retire SPM43 Retire Test Room?' appears.
 Step 5: A green 'Venue retired' message reads 'No approved bookings were affected, so nobody needed to be notified.' and a 'Retired' label appears beside the venue's name.
@@ -8843,7 +8845,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -8875,7 +8877,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 4: A dialog titled 'Retire SPM43 Retire Test Room?' appears.
 Step 5: A green 'Venue retired' message reads 'No approved bookings were affected, so nobody needed to be notified.' and a 'Retired' label appears beside the venue's name.
@@ -8947,7 +8949,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 4: A dialog titled 'Retire SPM43 Retire Test Room?' appears.
 Step 5: A green 'Venue retired' message reads 'No approved bookings were affected, so nobody needed to be notified.' and a 'Retired' label appears beside the venue's name.
@@ -10025,7 +10027,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC15</t>
         </is>
@@ -10037,7 +10039,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Policy Briefing' (status Under review, 09:00-12:00 on 18 May 2027) has a Pending request for Orchard Studio (ORC-STU) on 18 May 2027, AM. The app no longer lets a Coordinator make a request before the event is approved (SPM-54), so this one is created by the fixture script and stands for a request made before that rule.
@@ -10052,7 +10054,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -10067,7 +10069,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Policy Briefing at Orchard Studio (ORC-STU), 18 May 2027, AM
 Event status: Under review</t>
@@ -10080,7 +10082,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 3: There is no card for 'SPM43 Policy Briefing', although its request is Pending - a request waits for its event to be approved before Venue Staff see it.
 Step 4: There is no such card: every request listed belongs to an event that is past approval.</t>
@@ -10093,7 +10095,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -10125,7 +10127,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 3: There is no card for 'SPM43 Policy Briefing', although its request is Pending - a request waits for its event to be approved before Venue Staff see it.
 Step 4: There is no such card: every request listed belongs to an event that is past approval.</t>
@@ -10193,7 +10195,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 3: There is no card for 'SPM43 Policy Briefing', although its request is Pending - a request waits for its event to be approved before Venue Staff see it.
 Step 4: There is no such card: every request listed belongs to an event that is past approval.</t>
@@ -11260,7 +11262,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC05</t>
         </is>
@@ -11272,7 +11274,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Board Strategy Day' has an Approved booking at Marina Auditorium (MAR-AUD, setup 60 min, teardown 30 min) on 7 May 2027, AM + PM, so its turnaround takes 7 May Night. 'SPM43 Evening Recital' has a Pending request for Marina Auditorium on 7 May 2027, Night only.
@@ -11286,7 +11288,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -11301,7 +11303,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Pending: SPM43 Evening Recital, Marina Auditorium, 7 May 2027, Night
 Approved: SPM43 Board Strategy Day, Marina Auditorium, 7 May 2027, AM + PM (turnaround: 7 May Night)</t>
@@ -11314,7 +11316,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Step 3: Requested reads '7 May 2027 · Night (19:00–24:00)'. The badge reads 'Conflict'. The red message reads 'This overlaps an approved booking: EVT-… SPM43 Board Strategy Day holds Marina Auditorium on 7 May 2027 · AM, PM (07:00–18:00). The clash is through a setup or turnaround slot.'
 Step 4: The 'Approve' button is greyed out and nothing happens - no dialog opens.</t>
@@ -11327,7 +11329,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -11359,7 +11361,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Step 3: Requested reads '7 May 2027 · Night (19:00–24:00)'. The badge reads 'Conflict'. The red message reads 'This overlaps an approved booking: EVT-… SPM43 Board Strategy Day holds Marina Auditorium on 7 May 2027 · AM, PM (07:00–18:00). The clash is through a setup or turnaround slot.'
 Step 4: The 'Approve' button is greyed out and nothing happens - no dialog opens.</t>
@@ -11427,7 +11429,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Step 3: Requested reads '7 May 2027 · Night (19:00–24:00)'. The badge reads 'Conflict'. The red message reads 'This overlaps an approved booking: EVT-… SPM43 Board Strategy Day holds Marina Auditorium on 7 May 2027 · AM, PM (07:00–18:00). The clash is through a setup or turnaround slot.'
 Step 4: The 'Approve' button is greyed out and nothing happens - no dialog opens.</t>
@@ -12492,7 +12494,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">SPM-43-TC16
 </t>
@@ -12505,7 +12507,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Board Strategy Day' has an Approved booking at Marina Auditorium (MAR-AUD, setup 60 min, teardown 30 min) on 7 May 2027, AM + PM, so its turnaround takes 7 May Night. 'SPM43 Alumni Lecture' (status Planning, 14:00-17:00 on 8 May 2027) has a Pending request for Marina Auditorium on 8 May 2027, PM only; its own setup takes 8 May AM, the slot straight after that turnaround.
@@ -12521,7 +12523,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -12538,7 +12540,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Pending: SPM43 Alumni Lecture, Marina Auditorium, 8 May 2027, PM (setup: 8 May AM)
 Approved: SPM43 Board Strategy Day, Marina Auditorium, 7 May 2027, AM + PM (turnaround: 7 May Night)
@@ -12552,7 +12554,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Step 3: Requested reads '8 May 2027 · PM (13:00–18:00)', with 'Setup: 8 May 2027 AM (07:00–12:00)' and 'Turnaround: 8 May 2027 Night (19:00–24:00)' under it. The badge reads 'Pending', not 'Conflict', and the card has no red message.
 Step 4: The 'Approve this booking?' dialog opens, naming Marina Auditorium (MAR-AUD) and '8 May 2027 · PM (13:00–18:00)' - the request can be approved.
@@ -12567,7 +12569,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -12599,7 +12601,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Step 3: Requested reads '8 May 2027 · PM (13:00–18:00)', with 'Setup: 8 May 2027 AM (07:00–12:00)' and 'Turnaround: 8 May 2027 Night (19:00–24:00)' under it. The badge reads 'Pending', not 'Conflict', and the card has no red message.
 Step 4: The 'Approve this booking?' dialog opens, naming Marina Auditorium (MAR-AUD) and '8 May 2027 · PM (13:00–18:00)' - the request can be approved.
@@ -12669,7 +12671,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Step 3: Requested reads '8 May 2027 · PM (13:00–18:00)', with 'Setup: 8 May 2027 AM (07:00–12:00)' and 'Turnaround: 8 May 2027 Night (19:00–24:00)' under it. The badge reads 'Pending', not 'Conflict', and the card has no red message.
 Step 4: The 'Approve this booking?' dialog opens, naming Marina Auditorium (MAR-AUD) and '8 May 2027 · PM (13:00–18:00)' - the request can be approved.
@@ -13724,43 +13726,43 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Question / ambiguity for the PO or developer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="2" ht="111.75" customHeight="1" s="21">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>Reverting: a case that approves or rejects says so in its Preconditions ('This case changes data: run npm run fixtures:spm43 once when you finish testing …'). That command is the only reset needed and is never a reseed - it resets only the 'SPM43 …' events in place (their booking requests and decisions are dropped and recreated; each event keeps its EVT- reference), makes 'SPM43 Retire Test Room' active again and resets 'SPM43 Maintenance Room' to its one maintenance period. Nothing outside the SPM43 test data is changed by any case.</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n"/>
+      <c r="C2" s="25" t="n"/>
     </row>
     <row r="3" ht="84.75" customHeight="1" s="21">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Fixtures: scripts/seed-spm43.ts creates thirteen 'SPM43 …' events in May 2027, on base-seed venues plus the two test venues SPM43-MNT and SPM43-RET; prisma/seed.ts creates the same rows. Each event keeps its EVT- reference between runs on one database, but the number differs from one database to another, so the cases name events by title and never ask the tester to type an event address.</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n"/>
+      <c r="C3" s="25" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="21"/>
     <row r="22" ht="15.75" customHeight="1" s="21"/>
@@ -14783,7 +14785,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC01</t>
         </is>
@@ -14795,7 +14797,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Leadership Offsite' (status Planning, client Meridian Financial Group, coordinator Daniel Tan, 100 people, Theatre, 09:00-17:00 on 4 May 2027) has a Pending request for Orchard Seminar Room (ORC-SEM, setup 60 min, teardown 30 min). 'SPM43 Board Strategy Day' has a booking at Marina Auditorium that is already Approved.
@@ -14809,7 +14811,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -14824,7 +14826,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Leadership Offsite at Orchard Seminar Room (ORC-SEM), 4 May 2027, AM + PM
 Venue requirements: Lectern and two handheld microphones.</t>
@@ -14837,7 +14839,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 2: The 'Booking Requests' page opens with one card per pending request.
 Step 3: The card is headed 'Orchard Seminar Room (ORC-SEM)' with 'for EVT-… SPM43 Leadership Offsite · Meridian Financial Group' and the badge 'Pending'. It shows Requested '4 May 2027 · AM, PM (07:00–18:00)' with 'Setup: 3 May 2027 Night (19:00–24:00)' and 'Turnaround: 4 May 2027 Night (19:00–24:00)'; Event time '4 May 2027, 09:00–17:00'; Layout 'Theatre'; Expected attendance '100'; Venue requirements 'Lectern and two handheld microphones.'; Requested by 'Daniel Tan' with 'Event is Planning'. It has the buttons 'Approve' and 'Reject with a reason'.
@@ -14851,7 +14853,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -14883,7 +14885,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 2: The 'Booking Requests' page opens with one card per pending request.
 Step 3: The card is headed 'Orchard Seminar Room (ORC-SEM)' with 'for EVT-… SPM43 Leadership Offsite · Meridian Financial Group' and the badge 'Pending'. It shows Requested '4 May 2027 · AM, PM (07:00–18:00)' with 'Setup: 3 May 2027 Night (19:00–24:00)' and 'Turnaround: 4 May 2027 Night (19:00–24:00)'; Event time '4 May 2027, 09:00–17:00'; Layout 'Theatre'; Expected attendance '100'; Venue requirements 'Lectern and two handheld microphones.'; Requested by 'Daniel Tan' with 'Event is Planning'. It has the buttons 'Approve' and 'Reject with a reason'.
@@ -14952,7 +14954,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 2: The 'Booking Requests' page opens with one card per pending request.
 Step 3: The card is headed 'Orchard Seminar Room (ORC-SEM)' with 'for EVT-… SPM43 Leadership Offsite · Meridian Financial Group' and the badge 'Pending'. It shows Requested '4 May 2027 · AM, PM (07:00–18:00)' with 'Setup: 3 May 2027 Night (19:00–24:00)' and 'Turnaround: 4 May 2027 Night (19:00–24:00)'; Event time '4 May 2027, 09:00–17:00'; Layout 'Theatre'; Expected attendance '100'; Venue requirements 'Lectern and two handheld microphones.'; Requested by 'Daniel Tan' with 'Event is Planning'. It has the buttons 'Approve' and 'Reject with a reason'.
@@ -16027,7 +16029,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC02</t>
         </is>
@@ -16039,7 +16041,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Two-Day Forum' (status Planning, 60 people, Theatre, 11 May 2027 09:00 to 12 May 2027 17:00) has a session 'Day 2' (30 people, Classroom, 14:00-17:00 on 12 May 2027) with a Pending request for Jurong Training Room (JUR-TRN, setup 45 min, teardown 30 min).
@@ -16053,7 +16055,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -16067,7 +16069,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Two-Day Forum, session Day 2, at Jurong Training Room (JUR-TRN), 12 May 2027, PM
 Venue requirements: Tables in rows, power at every seat.</t>
@@ -16080,7 +16082,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 3: The card shows 'Session: Day 2'. Requested is '12 May 2027 · PM (13:00–18:00)' with 'Setup: 12 May 2027 AM (07:00–12:00)' and 'Turnaround: 12 May 2027 Night (19:00–24:00)'. The time is labelled 'Session time' and reads '12 May 2027, 14:00–17:00' (not the event's two days). Layout is 'Classroom' and Expected attendance is '30' (the session's, not the event's Theatre and 60). Venue requirements is 'Tables in rows, power at every seat.' and 'Event is Planning' is shown under Requested by.</t>
         </is>
@@ -16092,7 +16094,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -16124,7 +16126,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 3: The card shows 'Session: Day 2'. Requested is '12 May 2027 · PM (13:00–18:00)' with 'Setup: 12 May 2027 AM (07:00–12:00)' and 'Turnaround: 12 May 2027 Night (19:00–24:00)'. The time is labelled 'Session time' and reads '12 May 2027, 14:00–17:00' (not the event's two days). Layout is 'Classroom' and Expected attendance is '30' (the session's, not the event's Theatre and 60). Venue requirements is 'Tables in rows, power at every seat.' and 'Event is Planning' is shown under Requested by.</t>
         </is>
@@ -16191,7 +16193,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 3: The card shows 'Session: Day 2'. Requested is '12 May 2027 · PM (13:00–18:00)' with 'Setup: 12 May 2027 AM (07:00–12:00)' and 'Turnaround: 12 May 2027 Night (19:00–24:00)'. The time is labelled 'Session time' and reads '12 May 2027, 14:00–17:00' (not the event's two days). Layout is 'Classroom' and Expected attendance is '30' (the session's, not the event's Theatre and 60). Venue requirements is 'Tables in rows, power at every seat.' and 'Event is Planning' is shown under Requested by.</t>
         </is>
@@ -17264,7 +17266,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC03</t>
         </is>
@@ -17276,7 +17278,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Leadership Offsite' (status Planning, coordinator Daniel Tan, 09:00-17:00 on 4 May 2027) has a Pending request for Orchard Seminar Room (ORC-SEM, setup 60 min, teardown 30 min), AM + PM.
@@ -17291,7 +17293,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -17314,7 +17316,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Leadership Offsite at Orchard Seminar Room (ORC-SEM), 4 May 2027, AM + PM</t>
         </is>
@@ -17326,7 +17328,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 3: A dialog titled 'Approve this booking?' appears. It says this books Orchard Seminar Room (ORC-SEM) for SPM43 Leadership Offsite on '4 May 2027 · AM, PM (07:00–18:00)', and has the buttons 'Cancel' and 'Approve'.
 Step 4: The dialog closes and a green 'Booking approved' message appears, naming Orchard Seminar Room (ORC-SEM), SPM43 Leadership Offsite and '4 May 2027 · AM, PM (07:00–18:00)'.
@@ -17343,7 +17345,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -17375,7 +17377,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 3: A dialog titled 'Approve this booking?' appears. It says this books Orchard Seminar Room (ORC-SEM) for SPM43 Leadership Offsite on '4 May 2027 · AM, PM (07:00–18:00)', and has the buttons 'Cancel' and 'Approve'.
 Step 4: The dialog closes and a green 'Booking approved' message appears, naming Orchard Seminar Room (ORC-SEM), SPM43 Leadership Offsite and '4 May 2027 · AM, PM (07:00–18:00)'.
@@ -17447,7 +17449,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 3: A dialog titled 'Approve this booking?' appears. It says this books Orchard Seminar Room (ORC-SEM) for SPM43 Leadership Offsite on '4 May 2027 · AM, PM (07:00–18:00)', and has the buttons 'Cancel' and 'Approve'.
 Step 4: The dialog closes and a green 'Booking approved' message appears, naming Orchard Seminar Room (ORC-SEM), SPM43 Leadership Offsite and '4 May 2027 · AM, PM (07:00–18:00)'.
@@ -18525,7 +18527,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC04</t>
         </is>
@@ -18537,7 +18539,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Design Workshop' and 'SPM43 Coding Workshop' (both status Planning) each have a Pending request for Orchard Studio (ORC-STU) on 10 May 2027, PM.
@@ -18552,7 +18554,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -18571,7 +18573,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Approved first: SPM43 Design Workshop, Orchard Studio (ORC-STU), 10 May 2027, PM
 Left pending: SPM43 Coding Workshop, same room, date and slot</t>
@@ -18584,7 +18586,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 3: Both cards have the badge 'Pending' and an 'Approve' button that can be clicked.
 Step 5: A green 'Booking approved' message appears and the 'SPM43 Design Workshop' card leaves the list.
@@ -18600,7 +18602,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -18632,7 +18634,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 3: Both cards have the badge 'Pending' and an 'Approve' button that can be clicked.
 Step 5: A green 'Booking approved' message appears and the 'SPM43 Design Workshop' card leaves the list.
@@ -18703,7 +18705,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 3: Both cards have the badge 'Pending' and an 'Approve' button that can be clicked.
 Step 5: A green 'Booking approved' message appears and the 'SPM43 Design Workshop' card leaves the list.
@@ -19780,7 +19782,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC06</t>
         </is>
@@ -19792,7 +19794,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Cancelled Launch' (status Cancelled) still has a Pending request for Changi Conference Centre (CBP-CONF) on 13 May 2027, AM + PM.
@@ -19806,7 +19808,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -19822,7 +19824,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Cancelled Launch at Changi Conference Centre (CBP-CONF), 13 May 2027, AM + PM
 Event status: Cancelled</t>
@@ -19835,7 +19837,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 3: The card shows 'Event is Cancelled'.
 Step 5: The dialog closes. No 'Booking approved' message appears; the card shows the red message 'A booking cannot be approved for a completed, cancelled or rejected event. Reject it instead.' and stays in the list with the badge 'Pending'.</t>
@@ -19848,7 +19850,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -19880,7 +19882,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 3: The card shows 'Event is Cancelled'.
 Step 5: The dialog closes. No 'Booking approved' message appears; the card shows the red message 'A booking cannot be approved for a completed, cancelled or rejected event. Reject it instead.' and stays in the list with the badge 'Pending'.</t>
@@ -19948,7 +19950,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 3: The card shows 'Event is Cancelled'.
 Step 5: The dialog closes. No 'Booking approved' message appears; the card shows the red message 'A booking cannot be approved for a completed, cancelled or rejected event. Reject it instead.' and stays in the list with the badge 'Pending'.</t>
@@ -21022,7 +21024,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC07</t>
         </is>
@@ -21034,7 +21036,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Product Briefing' has a Pending request for Marina Auditorium (MAR-AUD) on 5 May 2027, PM.
@@ -21048,7 +21050,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -21065,7 +21067,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Attempt 1: reason empty
 Attempt 2: reason is three spaces</t>
@@ -21078,7 +21080,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 3: A form opens on the card with 'Reason for rejection' (marked required), 'Suggest another venue' showing 'No venue suggested', 'Alternative arrangement', and the buttons 'Reject request' and 'Cancel'.
 Step 4: 'A reason is required when rejecting. The Coordinator sees this message.' appears under 'Reason for rejection'. The request is not rejected.
@@ -21093,7 +21095,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -21125,7 +21127,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 3: A form opens on the card with 'Reason for rejection' (marked required), 'Suggest another venue' showing 'No venue suggested', 'Alternative arrangement', and the buttons 'Reject request' and 'Cancel'.
 Step 4: 'A reason is required when rejecting. The Coordinator sees this message.' appears under 'Reason for rejection'. The request is not rejected.
@@ -21195,7 +21197,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 3: A form opens on the card with 'Reason for rejection' (marked required), 'Suggest another venue' showing 'No venue suggested', 'Alternative arrangement', and the buttons 'Reject request' and 'Cancel'.
 Step 4: 'A reason is required when rejecting. The Coordinator sees this message.' appears under 'Reason for rejection'. The request is not rejected.
@@ -22271,7 +22273,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>SPM-43-TC08</t>
         </is>
@@ -22283,7 +22285,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff Marcus Wong (marcus.wong@connectsphere.com / password123).
 Seed: 'SPM43 Product Briefing' (status Planning, coordinator Daniel Tan) has a Pending request for Marina Auditorium (MAR-AUD) on 5 May 2027, PM.
@@ -22298,7 +22300,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com / password123
 2. Click 'Booking Requests' in the sidebar
@@ -22319,7 +22321,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Request: SPM43 Product Briefing at Marina Auditorium (MAR-AUD), 5 May 2027, PM
 Reason for rejection: Auditorium is closed for stage repairs that week.
@@ -22334,7 +22336,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Step 5: A green 'Booking request rejected' message appears, naming Marina Auditorium (MAR-AUD), SPM43 Product Briefing and '5 May 2027 · PM (13:00–18:00)'.
 Step 6: The card is no longer in the list.
@@ -22348,7 +22350,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -22380,7 +22382,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Step 5: A green 'Booking request rejected' message appears, naming Marina Auditorium (MAR-AUD), SPM43 Product Briefing and '5 May 2027 · PM (13:00–18:00)'.
 Step 6: The card is no longer in the list.
@@ -22449,7 +22451,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Step 5: A green 'Booking request rejected' message appears, naming Marina Auditorium (MAR-AUD), SPM43 Product Briefing and '5 May 2027 · PM (13:00–18:00)'.
 Step 6: The card is no longer in the list.

--- a/docs/test-cases/SPM-43_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-43_Test_Cases.xlsx
@@ -815,7 +815,7 @@
       <c r="H9" s="25" t="n"/>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t>#128 (Week 7 #1)</t>
+          <t>#128 (Week 7 #1); #103</t>
         </is>
       </c>
     </row>
@@ -1249,8 +1249,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="15.75" customHeight="1" s="21">
       <c r="A22" s="24" t="inlineStr">
         <is>
@@ -19761,10 +19759,11 @@
     <col width="12.63" customWidth="1" style="21" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="90" customHeight="1" s="21">
+    <row r="1" ht="154" customHeight="1" s="21">
       <c r="A1" s="26" t="inlineStr">
         <is>
-          <t>v2 (2026-10-19): Venue bookings are now made for a start and end time on a 15-minute grid (SPM-93, discussion #128, Week 7 Change #1). Read every AM / PM / Night slot in this case as the event's (or session's) own start and end times; setup and turnaround are the venue's minutes either side, not whole slots, and the calendar has one Schedule column instead of slot columns. The behaviour this case checks is unchanged.</t>
+          <t>v2 (2026-10-19): Venue bookings are now made for a start and end time on a 15-minute grid (SPM-93, discussion #128, Week 7 Change #1). Read every AM / PM / Night slot in this case as the event's (or session's) own start and end times; setup and turnaround are the venue's minutes either side, not whole slots, and the calendar has one Schedule column instead of slot columns. The behaviour this case checks is unchanged.
+v3 (2026-10-23): Step 5's message now reads 'A booking cannot be approved for a completed, cancelled, rejected or withdrawn event. Reject it instead.' instead of 'A booking cannot be approved for a completed, cancelled or rejected event. Reject it instead.' (SPM-59, discussion #103: the messages that refuse an action on a closed event now name withdrawn events too). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-43_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-43_Test_Cases.xlsx
@@ -815,7 +815,7 @@
       <c r="H9" s="25" t="n"/>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t>#128 (Week 7 #1); #103</t>
+          <t>#128 (Week 7 #1)</t>
         </is>
       </c>
     </row>
@@ -1249,6 +1249,8 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="15.75" customHeight="1" s="21">
       <c r="A22" s="24" t="inlineStr">
         <is>
@@ -19759,11 +19761,10 @@
     <col width="12.63" customWidth="1" style="21" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="154" customHeight="1" s="21">
+    <row r="1" ht="90" customHeight="1" s="21">
       <c r="A1" s="26" t="inlineStr">
         <is>
-          <t>v2 (2026-10-19): Venue bookings are now made for a start and end time on a 15-minute grid (SPM-93, discussion #128, Week 7 Change #1). Read every AM / PM / Night slot in this case as the event's (or session's) own start and end times; setup and turnaround are the venue's minutes either side, not whole slots, and the calendar has one Schedule column instead of slot columns. The behaviour this case checks is unchanged.
-v3 (2026-10-23): Step 5's message now reads 'A booking cannot be approved for a completed, cancelled, rejected or withdrawn event. Reject it instead.' instead of 'A booking cannot be approved for a completed, cancelled or rejected event. Reject it instead.' (SPM-59, discussion #103: the messages that refuse an action on a closed event now name withdrawn events too). Read the expected result with the new wording. The behaviour this case checks is unchanged.</t>
+          <t>v2 (2026-10-19): Venue bookings are now made for a start and end time on a 15-minute grid (SPM-93, discussion #128, Week 7 Change #1). Read every AM / PM / Night slot in this case as the event's (or session's) own start and end times; setup and turnaround are the venue's minutes either side, not whole slots, and the calendar has one Schedule column instead of slot columns. The behaviour this case checks is unchanged.</t>
         </is>
       </c>
     </row>
